--- a/Tests/Validation/Wheat/data/FAR HYC W18-02-2a.xlsx
+++ b/Tests/Validation/Wheat/data/FAR HYC W18-02-2a.xlsx
@@ -1,32 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Observed" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observed" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,16 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,136 +430,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z126"/>
+  <dimension ref="A1:V126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>SimulationName</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Clock.Today</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.CurrentStageName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Cultivar</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Potential</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>GS.se</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Phenology.Zadok.Stage</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt.se</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Population</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Population.se</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Population</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Population.se</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI.se</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.Height</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.Height.se</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density.se</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Wheat.Grain.Moisture</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Grain.WaterContent</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Moisture.se</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein.se</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings.se</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt.se</t>
         </is>
@@ -558,37 +551,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAnapurna</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="3" t="n">
         <v>43270</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0184842275106824</v>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.0184842275106824</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -597,10 +578,6 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -608,37 +585,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAnapurna</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>43290</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.00912870929175274</v>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.00912870929175274</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -647,10 +612,6 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -658,37 +619,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAnapurna</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>43306</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>0.6775</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.00629152869605893</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>0.6775</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.00629152869605893</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -697,10 +646,6 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -708,37 +653,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAnapurna</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="3" t="n">
         <v>43341</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>0.7925</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.00750000000000001</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>0.7925</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.00750000000000001</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -747,10 +680,6 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -758,37 +687,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAnapurna</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="3" t="n">
         <v>43381</v>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.00288675134594813</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.00288675134594813</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -797,10 +714,6 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -808,31 +721,17 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAnapurna</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="3" t="n">
         <v>43399</v>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="D7" t="n">
         <v>59</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -847,10 +746,6 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -858,33 +753,21 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAnapurna</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="3" t="n">
         <v>43413</v>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>1130.50400735522</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.05118136500608</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
-        <v>1130.50400735522</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.05118136500608</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -897,10 +780,6 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -908,49 +787,33 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAnapurna</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="3" t="n">
         <v>43440</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>87.0833333333333</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.26640112823702</v>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
-        <v>87.0833333333333</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.26640112823702</v>
-      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -958,37 +821,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAnapurna</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="3" t="n">
         <v>43446</v>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0110867789130417</v>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>0.4175</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.0110867789130417</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -997,10 +848,6 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1008,37 +855,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAnapurna</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="3" t="n">
         <v>43455</v>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0210158670215308</v>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.0210158670215308</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -1047,10 +882,6 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1058,7 +889,7 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAnapurna</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="3" t="n">
         <v>43480</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -1066,29 +897,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>2448.94103102816</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.47884797726677</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="n">
-        <v>2448.94103102816</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.47884797726677</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1101,10 +920,6 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1112,7 +927,7 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAnapurna</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="3" t="n">
         <v>43495</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -1120,59 +935,43 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>81.854</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0850999412455735</v>
+      </c>
+      <c r="O13" t="n">
+        <v>10.775</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.125</v>
+      </c>
       <c r="Q13" t="n">
-        <v>81.854</v>
+        <v>11.975</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0850999412455735</v>
+        <v>0.262599187609812</v>
       </c>
       <c r="S13" t="n">
-        <v>10.775</v>
+        <v>2.05053768546608</v>
       </c>
       <c r="T13" t="n">
-        <v>0.125</v>
+        <v>0.208435879536425</v>
       </c>
       <c r="U13" t="n">
-        <v>11.975</v>
+        <v>1064.1207799453</v>
       </c>
       <c r="V13" t="n">
-        <v>0.262599187609812</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.05053768546608</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.208435879536425</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1064.1207799453</v>
-      </c>
-      <c r="Z13" t="n">
         <v>0.162446825627782</v>
       </c>
     </row>
@@ -1182,37 +981,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAccroc</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="3" t="n">
         <v>43270</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.008539125638299659</v>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>0.4125</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.008539125638299659</v>
-      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -1221,10 +1008,6 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1232,37 +1015,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAccroc</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="3" t="n">
         <v>43290</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0103077640640441</v>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.0103077640640441</v>
-      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
@@ -1271,10 +1042,6 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1282,37 +1049,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAccroc</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="3" t="n">
         <v>43306</v>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.00853912563829964</v>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.00853912563829964</v>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -1321,10 +1076,6 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1332,37 +1083,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAccroc</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="3" t="n">
         <v>43341</v>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>0.7925</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.008539125638299659</v>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>0.7925</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.008539125638299659</v>
-      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
@@ -1371,10 +1110,6 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1382,37 +1117,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAccroc</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="3" t="n">
         <v>43381</v>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.00866025403784439</v>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.00866025403784439</v>
-      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
@@ -1421,10 +1144,6 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1432,31 +1151,17 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAccroc</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="3" t="n">
         <v>43399</v>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
+      <c r="D19" t="n">
         <v>59</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1471,10 +1176,6 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1482,33 +1183,21 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAccroc</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="3" t="n">
         <v>43413</v>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>1596.21067091586</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.633891238114164</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="n">
-        <v>1596.21067091586</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.633891238114164</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -1521,10 +1210,6 @@
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1532,49 +1217,33 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAccroc</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="3" t="n">
         <v>43440</v>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.14033140389953</v>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>84.75</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.14033140389953</v>
-      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1582,37 +1251,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAccroc</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="3" t="n">
         <v>43446</v>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.0259406373604556</v>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
-        <v>0.3275</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.0259406373604556</v>
-      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
@@ -1621,10 +1278,6 @@
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1632,37 +1285,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAccroc</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="3" t="n">
         <v>43455</v>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.0118145390656315</v>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.0118145390656315</v>
-      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
@@ -1671,10 +1312,6 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1682,7 +1319,7 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAccroc</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="3" t="n">
         <v>43480</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1690,29 +1327,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>2499.18781427679</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.75524224484706</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
-        <v>2499.18781427679</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.75524224484706</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
@@ -1725,10 +1350,6 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1736,7 +1357,7 @@
           <t>FAR HYC W18-02-2aPGRPGRCvAccroc</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="3" t="n">
         <v>43495</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1744,59 +1365,43 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>79.8635</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.328208648068063</v>
+      </c>
+      <c r="O25" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.158113883008418</v>
+      </c>
       <c r="Q25" t="n">
-        <v>79.8635</v>
+        <v>10.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0.328208648068063</v>
+        <v>0.432049379893857</v>
       </c>
       <c r="S25" t="n">
-        <v>10.7</v>
+        <v>1.13791168607129</v>
       </c>
       <c r="T25" t="n">
-        <v>0.158113883008418</v>
+        <v>0.0432099731699114</v>
       </c>
       <c r="U25" t="n">
-        <v>10.4</v>
+        <v>1054.41465465241</v>
       </c>
       <c r="V25" t="n">
-        <v>0.432049379893857</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.13791168607129</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.0432099731699114</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1054.41465465241</v>
-      </c>
-      <c r="Z25" t="n">
         <v>0.353583202125724</v>
       </c>
     </row>
@@ -1806,37 +1411,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvKittyhawk</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="3" t="n">
         <v>43270</v>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.0239356776939084</v>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
-        <v>0.4075</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.0239356776939084</v>
-      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -1845,10 +1438,6 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1856,37 +1445,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvKittyhawk</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="3" t="n">
         <v>43290</v>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.009574271077563361</v>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.009574271077563361</v>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -1895,10 +1472,6 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1906,37 +1479,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvKittyhawk</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="3" t="n">
         <v>43306</v>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.0193649167310371</v>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.0193649167310371</v>
-      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
@@ -1945,10 +1506,6 @@
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1956,37 +1513,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvKittyhawk</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="3" t="n">
         <v>43341</v>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0184842275106824</v>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.0184842275106824</v>
-      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
@@ -1995,10 +1540,6 @@
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2006,37 +1547,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvKittyhawk</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="3" t="n">
         <v>43381</v>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.7425</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0143614066163451</v>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
-        <v>0.7425</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.0143614066163451</v>
-      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
@@ -2045,10 +1574,6 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2056,31 +1581,17 @@
           <t>FAR HYC W18-02-2aPGRPGRCvKittyhawk</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="3" t="n">
         <v>43399</v>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
+      <c r="D31" t="n">
         <v>57</v>
       </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -2095,10 +1606,6 @@
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2106,33 +1613,21 @@
           <t>FAR HYC W18-02-2aPGRPGRCvKittyhawk</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="3" t="n">
         <v>43413</v>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>1335.02437201241</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.531969542213469</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="n">
-        <v>1335.02437201241</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.531969542213469</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -2145,10 +1640,6 @@
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2156,49 +1647,33 @@
           <t>FAR HYC W18-02-2aPGRPGRCvKittyhawk</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="3" t="n">
         <v>43440</v>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.65201896679992</v>
+      </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="n">
-        <v>89.25</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.65201896679992</v>
-      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2206,37 +1681,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvKittyhawk</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="3" t="n">
         <v>43446</v>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.0165201896679992</v>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
-        <v>0.4725</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.0165201896679992</v>
-      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
@@ -2245,10 +1708,6 @@
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2256,37 +1715,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvKittyhawk</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="3" t="n">
         <v>43455</v>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.0132287565553229</v>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.0132287565553229</v>
-      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
@@ -2295,10 +1742,6 @@
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2306,7 +1749,7 @@
           <t>FAR HYC W18-02-2aPGRPGRCvKittyhawk</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="3" t="n">
         <v>43480</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -2314,29 +1757,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>2230.18437514743</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.615925323847941</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="n">
-        <v>2230.18437514743</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.615925323847941</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -2349,10 +1780,6 @@
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2360,7 +1787,7 @@
           <t>FAR HYC W18-02-2aPGRPGRCvKittyhawk</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="3" t="n">
         <v>43495</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -2368,59 +1795,43 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>82.85899999999999</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.390490716919111</v>
+      </c>
+      <c r="O37" t="n">
+        <v>10.875</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.07500000000000021</v>
+      </c>
       <c r="Q37" t="n">
-        <v>82.85899999999999</v>
+        <v>12.7</v>
       </c>
       <c r="R37" t="n">
-        <v>0.390490716919111</v>
+        <v>0.291547594742265</v>
       </c>
       <c r="S37" t="n">
-        <v>10.875</v>
+        <v>1.77970847722532</v>
       </c>
       <c r="T37" t="n">
-        <v>0.07500000000000021</v>
+        <v>0.15274774660944</v>
       </c>
       <c r="U37" t="n">
-        <v>12.7</v>
+        <v>766.529867470418</v>
       </c>
       <c r="V37" t="n">
-        <v>0.291547594742265</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.77970847722532</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.15274774660944</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>766.529867470418</v>
-      </c>
-      <c r="Z37" t="n">
         <v>0.274408522222168</v>
       </c>
     </row>
@@ -2430,37 +1841,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvRelay</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="3" t="n">
         <v>43270</v>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0270801280154532</v>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0.0270801280154532</v>
-      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
@@ -2469,10 +1868,6 @@
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2480,37 +1875,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvRelay</t>
         </is>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="3" t="n">
         <v>43290</v>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0165201896679992</v>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.0165201896679992</v>
-      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
@@ -2519,10 +1902,6 @@
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2530,37 +1909,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvRelay</t>
         </is>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="3" t="n">
         <v>43306</v>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>0.6825</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.0217466472511665</v>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="n">
-        <v>0.6825</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.0217466472511665</v>
-      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
@@ -2569,10 +1936,6 @@
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2580,37 +1943,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvRelay</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="3" t="n">
         <v>43341</v>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>0.7875</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.0188745860881769</v>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="n">
-        <v>0.7875</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0.0188745860881769</v>
-      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
@@ -2619,10 +1970,6 @@
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2630,37 +1977,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvRelay</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="3" t="n">
         <v>43381</v>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.0227303028283098</v>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.0227303028283098</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -2669,10 +2004,6 @@
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2680,31 +2011,17 @@
           <t>FAR HYC W18-02-2aPGRPGRCvRelay</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="3" t="n">
         <v>43399</v>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
+      <c r="D43" t="n">
         <v>37</v>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2719,10 +2036,6 @@
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2730,33 +2043,21 @@
           <t>FAR HYC W18-02-2aPGRPGRCvRelay</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="3" t="n">
         <v>43430</v>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>1610.78635953026</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.638349127251672</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="n">
-        <v>1610.78635953026</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.638349127251672</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
@@ -2769,10 +2070,6 @@
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2780,49 +2077,33 @@
           <t>FAR HYC W18-02-2aPGRPGRCvRelay</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="3" t="n">
         <v>43440</v>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+      <c r="K45" t="n">
+        <v>79.9166666666667</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.93110503770941</v>
+      </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="n">
-        <v>79.9166666666667</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.93110503770941</v>
-      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2830,37 +2111,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvRelay</t>
         </is>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="3" t="n">
         <v>43446</v>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>0.6375</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.00853912563829967</v>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="n">
-        <v>0.6375</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.00853912563829967</v>
-      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
@@ -2869,10 +2138,6 @@
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2880,37 +2145,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvRelay</t>
         </is>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="3" t="n">
         <v>43455</v>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.00912870929175278</v>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.00912870929175278</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
@@ -2919,10 +2172,6 @@
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2930,7 +2179,7 @@
           <t>FAR HYC W18-02-2aPGRPGRCvRelay</t>
         </is>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="3" t="n">
         <v>43480</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -2938,29 +2187,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>2662.55252798661</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.922749224764879</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="n">
-        <v>2662.55252798661</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.922749224764879</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -2973,10 +2210,6 @@
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2984,7 +2217,7 @@
           <t>FAR HYC W18-02-2aPGRPGRCvRelay</t>
         </is>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="3" t="n">
         <v>43495</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -2992,59 +2225,43 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+      <c r="M49" t="n">
+        <v>74.749</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1.80224794816548</v>
+      </c>
+      <c r="O49" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.104083299973307</v>
+      </c>
       <c r="Q49" t="n">
-        <v>74.749</v>
+        <v>11</v>
       </c>
       <c r="R49" t="n">
-        <v>1.80224794816548</v>
+        <v>0.374165738677394</v>
       </c>
       <c r="S49" t="n">
-        <v>10.15</v>
+        <v>3.85278069044004</v>
       </c>
       <c r="T49" t="n">
-        <v>0.104083299973307</v>
+        <v>0.388607651739291</v>
       </c>
       <c r="U49" t="n">
-        <v>11</v>
+        <v>790.015570284424</v>
       </c>
       <c r="V49" t="n">
-        <v>0.374165738677394</v>
-      </c>
-      <c r="W49" t="n">
-        <v>3.85278069044004</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0.388607651739291</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>790.015570284424</v>
-      </c>
-      <c r="Z49" t="n">
         <v>0.312071574100325</v>
       </c>
     </row>
@@ -3054,37 +2271,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvCalabro</t>
         </is>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="3" t="n">
         <v>43270</v>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.0131497781983829</v>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="n">
-        <v>0.4325</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0.0131497781983829</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
@@ -3093,10 +2298,6 @@
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3104,37 +2305,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvCalabro</t>
         </is>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="3" t="n">
         <v>43290</v>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.00707106781186546</v>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.00707106781186546</v>
-      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
@@ -3143,10 +2332,6 @@
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3154,37 +2339,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvCalabro</t>
         </is>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="3" t="n">
         <v>43306</v>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>0.6775</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.008539125638299651</v>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="n">
-        <v>0.6775</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0.008539125638299651</v>
-      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
@@ -3193,10 +2366,6 @@
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3204,37 +2373,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvCalabro</t>
         </is>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="3" t="n">
         <v>43341</v>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.0119023807142381</v>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0.0119023807142381</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
@@ -3243,10 +2400,6 @@
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3254,37 +2407,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvCalabro</t>
         </is>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="3" t="n">
         <v>43381</v>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.0125830573921179</v>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0.0125830573921179</v>
-      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
@@ -3293,10 +2434,6 @@
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3304,31 +2441,17 @@
           <t>FAR HYC W18-02-2aPGRPGRCvCalabro</t>
         </is>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="3" t="n">
         <v>43399</v>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
+      <c r="D55" t="n">
         <v>53</v>
       </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3343,10 +2466,6 @@
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3354,33 +2473,21 @@
           <t>FAR HYC W18-02-2aPGRPGRCvCalabro</t>
         </is>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="3" t="n">
         <v>43430</v>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>1953.86265942029</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.10669526826041</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="n">
-        <v>1953.86265942029</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.10669526826041</v>
-      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
@@ -3393,10 +2500,6 @@
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3404,49 +2507,33 @@
           <t>FAR HYC W18-02-2aPGRPGRCvCalabro</t>
         </is>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="3" t="n">
         <v>43440</v>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>85.3333333333333</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.70511213924698</v>
+      </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
-      <c r="O57" t="n">
-        <v>85.3333333333333</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1.70511213924698</v>
-      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3454,37 +2541,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvCalabro</t>
         </is>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="3" t="n">
         <v>43446</v>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.00707106781186548</v>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0.00707106781186548</v>
-      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
@@ -3493,10 +2568,6 @@
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3504,37 +2575,25 @@
           <t>FAR HYC W18-02-2aPGRPGRCvCalabro</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="3" t="n">
         <v>43455</v>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.0268871096748361</v>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="n">
-        <v>0.3575</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0.0268871096748361</v>
-      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
@@ -3543,10 +2602,6 @@
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3554,7 +2609,7 @@
           <t>FAR HYC W18-02-2aPGRPGRCvCalabro</t>
         </is>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="3" t="n">
         <v>43480</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -3562,29 +2617,17 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>2690.80762513898</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.754258728658369</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="n">
-        <v>2690.80762513898</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.754258728658369</v>
-      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
@@ -3597,10 +2640,6 @@
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3608,7 +2647,7 @@
           <t>FAR HYC W18-02-2aPGRPGRCvCalabro</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="3" t="n">
         <v>43495</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -3616,59 +2655,43 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>PGR</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="M61" t="n">
+        <v>80.215</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.228648930313118</v>
+      </c>
+      <c r="O61" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.108012344973464</v>
+      </c>
       <c r="Q61" t="n">
-        <v>80.215</v>
+        <v>10.75</v>
       </c>
       <c r="R61" t="n">
-        <v>0.228648930313118</v>
+        <v>0.262995563967658</v>
       </c>
       <c r="S61" t="n">
-        <v>10.7</v>
+        <v>1.95745966876892</v>
       </c>
       <c r="T61" t="n">
-        <v>0.108012344973464</v>
+        <v>0.116749591756155</v>
       </c>
       <c r="U61" t="n">
-        <v>10.75</v>
+        <v>1070.85386838918</v>
       </c>
       <c r="V61" t="n">
-        <v>0.262995563967658</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.95745966876892</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0.116749591756155</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1070.85386838918</v>
-      </c>
-      <c r="Z61" t="n">
         <v>0.183673116360481</v>
       </c>
     </row>
@@ -3678,31 +2701,23 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAnapurna</t>
         </is>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="3" t="n">
         <v>43237</v>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>156.875</v>
+      </c>
+      <c r="H62" t="n">
+        <v>13.5928519818322</v>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="n">
-        <v>156.875</v>
-      </c>
-      <c r="L62" t="n">
-        <v>13.5928519818322</v>
-      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
@@ -3713,10 +2728,6 @@
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3724,33 +2735,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAnapurna</t>
         </is>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="3" t="n">
         <v>43270</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.0225</v>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="n">
-        <v>0.4175</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0.0225</v>
-      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
@@ -3759,10 +2762,6 @@
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3770,33 +2769,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAnapurna</t>
         </is>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="3" t="n">
         <v>43290</v>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.00645497224367899</v>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0.00645497224367899</v>
-      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
@@ -3805,10 +2796,6 @@
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3816,33 +2803,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAnapurna</t>
         </is>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="3" t="n">
         <v>43306</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.01842778698958</v>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0.01842778698958</v>
-      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
@@ -3851,10 +2830,6 @@
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3862,33 +2837,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAnapurna</t>
         </is>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="3" t="n">
         <v>43341</v>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>0.7925</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.0103077640640442</v>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="n">
-        <v>0.7925</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0.0103077640640442</v>
-      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
@@ -3897,10 +2864,6 @@
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3908,29 +2871,21 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAnapurna</t>
         </is>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="3" t="n">
         <v>43364</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E67" t="n">
+        <v>395.646331541629</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.482066717388774</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="n">
-        <v>395.646331541629</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0.482066717388774</v>
-      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
@@ -3943,10 +2898,6 @@
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3954,33 +2905,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAnapurna</t>
         </is>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="3" t="n">
         <v>43381</v>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>0.7625</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.0103077640640442</v>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="n">
-        <v>0.7625</v>
-      </c>
-      <c r="N68" t="n">
-        <v>0.0103077640640442</v>
-      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
@@ -3989,10 +2932,6 @@
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4000,29 +2939,21 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAnapurna</t>
         </is>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="3" t="n">
         <v>43413</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E69" t="n">
+        <v>1415.71354113142</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.527075039811958</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="n">
-        <v>1415.71354113142</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0.527075039811958</v>
-      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
@@ -4035,10 +2966,6 @@
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4046,45 +2973,33 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAnapurna</t>
         </is>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="3" t="n">
         <v>43440</v>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="K70" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2.16185362851214</v>
+      </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="n">
-        <v>95.25</v>
-      </c>
-      <c r="P70" t="n">
-        <v>2.16185362851214</v>
-      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4092,33 +3007,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAnapurna</t>
         </is>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="3" t="n">
         <v>43446</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.0221735578260835</v>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0.0221735578260835</v>
-      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
@@ -4127,10 +3034,6 @@
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4138,33 +3041,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAnapurna</t>
         </is>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="3" t="n">
         <v>43455</v>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>0.2225</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.0149303940559741</v>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="n">
-        <v>0.2225</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0.0149303940559741</v>
-      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
@@ -4173,10 +3068,6 @@
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4184,7 +3075,7 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAnapurna</t>
         </is>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="3" t="n">
         <v>43480</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -4193,24 +3084,16 @@
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E73" t="n">
+        <v>2695.61044803244</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.30218373678965</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="n">
-        <v>2695.61044803244</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1.30218373678965</v>
-      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
@@ -4223,10 +3106,6 @@
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4234,7 +3113,7 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAnapurna</t>
         </is>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="3" t="n">
         <v>43495</v>
       </c>
       <c r="C74" t="inlineStr">
@@ -4243,54 +3122,42 @@
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Anapurna</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+      <c r="M74" t="n">
+        <v>81.2915</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.324413701930114</v>
+      </c>
+      <c r="O74" t="n">
+        <v>10.675</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.08539125638299649</v>
+      </c>
       <c r="Q74" t="n">
-        <v>81.2915</v>
+        <v>12.4</v>
       </c>
       <c r="R74" t="n">
-        <v>0.324413701930114</v>
+        <v>0.158113883008419</v>
       </c>
       <c r="S74" t="n">
-        <v>10.675</v>
+        <v>1.95070389474602</v>
       </c>
       <c r="T74" t="n">
-        <v>0.08539125638299649</v>
+        <v>0.15277960068756</v>
       </c>
       <c r="U74" t="n">
-        <v>12.4</v>
+        <v>1027.42923221596</v>
       </c>
       <c r="V74" t="n">
-        <v>0.158113883008419</v>
-      </c>
-      <c r="W74" t="n">
-        <v>1.95070389474602</v>
-      </c>
-      <c r="X74" t="n">
-        <v>0.15277960068756</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>1027.42923221596</v>
-      </c>
-      <c r="Z74" t="n">
         <v>0.15906860489822</v>
       </c>
     </row>
@@ -4300,31 +3167,23 @@
           <t>FAR HYC W18-02-2aPGRNoneCvKittyhawk</t>
         </is>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="3" t="n">
         <v>43237</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>16.551686721701</v>
+      </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="L75" t="n">
-        <v>16.551686721701</v>
-      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
@@ -4335,10 +3194,6 @@
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4346,33 +3201,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvKittyhawk</t>
         </is>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="3" t="n">
         <v>43270</v>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="I76" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.0103077640640441</v>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="n">
-        <v>0.4125</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0.0103077640640441</v>
-      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
@@ -4381,10 +3228,6 @@
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4392,33 +3235,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvKittyhawk</t>
         </is>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="3" t="n">
         <v>43290</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="I77" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.0168325082306035</v>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0.0168325082306035</v>
-      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
@@ -4427,10 +3262,6 @@
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4438,33 +3269,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvKittyhawk</t>
         </is>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="3" t="n">
         <v>43306</v>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+      <c r="I78" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.0254950975679639</v>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0.0254950975679639</v>
-      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
@@ -4473,10 +3296,6 @@
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4484,33 +3303,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvKittyhawk</t>
         </is>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="3" t="n">
         <v>43341</v>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="I79" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.0202072594216369</v>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0.0202072594216369</v>
-      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
@@ -4519,10 +3330,6 @@
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4530,29 +3337,21 @@
           <t>FAR HYC W18-02-2aPGRNoneCvKittyhawk</t>
         </is>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="3" t="n">
         <v>43364</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E80" t="n">
+        <v>432.857098838312</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.246219419885873</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="n">
-        <v>432.857098838312</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0.246219419885873</v>
-      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
@@ -4565,10 +3364,6 @@
       <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4576,33 +3371,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvKittyhawk</t>
         </is>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" s="3" t="n">
         <v>43381</v>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="I81" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.0225462487641145</v>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0.0225462487641145</v>
-      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
@@ -4611,10 +3398,6 @@
       <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4622,29 +3405,21 @@
           <t>FAR HYC W18-02-2aPGRNoneCvKittyhawk</t>
         </is>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" s="3" t="n">
         <v>43413</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E82" t="n">
+        <v>1180.98147205573</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.513884868905825</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
-      <c r="I82" t="n">
-        <v>1180.98147205573</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0.513884868905825</v>
-      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
@@ -4657,10 +3432,6 @@
       <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4668,45 +3439,33 @@
           <t>FAR HYC W18-02-2aPGRNoneCvKittyhawk</t>
         </is>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" s="3" t="n">
         <v>43440</v>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
+      <c r="K83" t="n">
+        <v>92.8333333333333</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1.06718737290547</v>
+      </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" t="n">
-        <v>92.8333333333333</v>
-      </c>
-      <c r="P83" t="n">
-        <v>1.06718737290547</v>
-      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4714,33 +3473,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvKittyhawk</t>
         </is>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" s="3" t="n">
         <v>43446</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="I84" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.0202072594216369</v>
+      </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0.0202072594216369</v>
-      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
@@ -4749,10 +3500,6 @@
       <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-      <c r="Z84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4760,33 +3507,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvKittyhawk</t>
         </is>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" s="3" t="n">
         <v>43455</v>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.0325</v>
+      </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" t="n">
-        <v>0.2775</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0.0325</v>
-      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
@@ -4795,10 +3534,6 @@
       <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4806,7 +3541,7 @@
           <t>FAR HYC W18-02-2aPGRNoneCvKittyhawk</t>
         </is>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" s="3" t="n">
         <v>43480</v>
       </c>
       <c r="C86" t="inlineStr">
@@ -4815,24 +3550,16 @@
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E86" t="n">
+        <v>2261.5813686304</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.8054668582714199</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="n">
-        <v>2261.5813686304</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0.8054668582714199</v>
-      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
@@ -4845,10 +3572,6 @@
       <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
-      <c r="Z86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4856,7 +3579,7 @@
           <t>FAR HYC W18-02-2aPGRNoneCvKittyhawk</t>
         </is>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" s="3" t="n">
         <v>43495</v>
       </c>
       <c r="C87" t="inlineStr">
@@ -4865,54 +3588,42 @@
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Kittyhawk</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
+      <c r="M87" t="n">
+        <v>82.374</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.301636646756763</v>
+      </c>
+      <c r="O87" t="n">
+        <v>10.875</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.125</v>
+      </c>
       <c r="Q87" t="n">
-        <v>82.374</v>
+        <v>13.075</v>
       </c>
       <c r="R87" t="n">
-        <v>0.301636646756763</v>
+        <v>0.39024564913227</v>
       </c>
       <c r="S87" t="n">
-        <v>10.875</v>
+        <v>1.64640059871448</v>
       </c>
       <c r="T87" t="n">
-        <v>0.125</v>
+        <v>0.0897976703681722</v>
       </c>
       <c r="U87" t="n">
-        <v>13.075</v>
+        <v>701.566277502384</v>
       </c>
       <c r="V87" t="n">
-        <v>0.39024564913227</v>
-      </c>
-      <c r="W87" t="n">
-        <v>1.64640059871448</v>
-      </c>
-      <c r="X87" t="n">
-        <v>0.0897976703681722</v>
-      </c>
-      <c r="Y87" t="n">
-        <v>701.566277502384</v>
-      </c>
-      <c r="Z87" t="n">
         <v>0.378443247305723</v>
       </c>
     </row>
@@ -4922,31 +3633,23 @@
           <t>FAR HYC W18-02-2aPGRNoneCvRelay</t>
         </is>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" s="3" t="n">
         <v>43237</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="n">
+        <v>151.875</v>
+      </c>
+      <c r="H88" t="n">
+        <v>10.6739070478746</v>
+      </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="n">
-        <v>151.875</v>
-      </c>
-      <c r="L88" t="n">
-        <v>10.6739070478746</v>
-      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
@@ -4957,10 +3660,6 @@
       <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
-      <c r="Z88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4968,33 +3667,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvRelay</t>
         </is>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" s="3" t="n">
         <v>43270</v>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="I89" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.0234520787991171</v>
+      </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0.0234520787991171</v>
-      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
@@ -5003,10 +3694,6 @@
       <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5014,33 +3701,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvRelay</t>
         </is>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" s="3" t="n">
         <v>43290</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+      <c r="I90" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.0125</v>
+      </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="n">
-        <v>0.8275</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0.0125</v>
-      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
@@ -5049,10 +3728,6 @@
       <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr"/>
-      <c r="Z90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5060,33 +3735,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvRelay</t>
         </is>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" s="3" t="n">
         <v>43306</v>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.0209662427090152</v>
+      </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
-      <c r="M91" t="n">
-        <v>0.7025</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0.0209662427090152</v>
-      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
@@ -5095,10 +3762,6 @@
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr"/>
-      <c r="Z91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5106,33 +3769,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvRelay</t>
         </is>
       </c>
-      <c r="B92" s="1" t="n">
+      <c r="B92" s="3" t="n">
         <v>43341</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+      <c r="I92" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.0193110503770941</v>
+      </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
-      <c r="M92" t="n">
-        <v>0.8075</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0.0193110503770941</v>
-      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
@@ -5141,10 +3796,6 @@
       <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr"/>
-      <c r="Z92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5152,29 +3803,21 @@
           <t>FAR HYC W18-02-2aPGRNoneCvRelay</t>
         </is>
       </c>
-      <c r="B93" s="1" t="n">
+      <c r="B93" s="3" t="n">
         <v>43364</v>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E93" t="n">
+        <v>265.789020039915</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.293428197823664</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="n">
-        <v>265.789020039915</v>
-      </c>
-      <c r="J93" t="n">
-        <v>0.293428197823664</v>
-      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
@@ -5187,10 +3830,6 @@
       <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
-      <c r="Y93" t="inlineStr"/>
-      <c r="Z93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5198,33 +3837,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvRelay</t>
         </is>
       </c>
-      <c r="B94" s="1" t="n">
+      <c r="B94" s="3" t="n">
         <v>43381</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+      <c r="I94" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.0184842275106824</v>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0.0184842275106824</v>
-      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
@@ -5233,10 +3864,6 @@
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
-      <c r="Y94" t="inlineStr"/>
-      <c r="Z94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5244,29 +3871,21 @@
           <t>FAR HYC W18-02-2aPGRNoneCvRelay</t>
         </is>
       </c>
-      <c r="B95" s="1" t="n">
+      <c r="B95" s="3" t="n">
         <v>43430</v>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E95" t="n">
+        <v>1975.38441795385</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.879363668485629</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="n">
-        <v>1975.38441795385</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0.879363668485629</v>
-      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
@@ -5279,10 +3898,6 @@
       <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr"/>
-      <c r="Z95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5290,45 +3905,33 @@
           <t>FAR HYC W18-02-2aPGRNoneCvRelay</t>
         </is>
       </c>
-      <c r="B96" s="1" t="n">
+      <c r="B96" s="3" t="n">
         <v>43440</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
+      <c r="K96" t="n">
+        <v>82.1666666666667</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1.84842275106824</v>
+      </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="n">
-        <v>82.1666666666667</v>
-      </c>
-      <c r="P96" t="n">
-        <v>1.84842275106824</v>
-      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr"/>
-      <c r="Z96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5336,33 +3939,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvRelay</t>
         </is>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" s="3" t="n">
         <v>43446</v>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="I97" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.00853912563829967</v>
+      </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
-      <c r="M97" t="n">
-        <v>0.6475</v>
-      </c>
-      <c r="N97" t="n">
-        <v>0.00853912563829967</v>
-      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
@@ -5371,10 +3966,6 @@
       <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr"/>
-      <c r="Z97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5382,33 +3973,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvRelay</t>
         </is>
       </c>
-      <c r="B98" s="1" t="n">
+      <c r="B98" s="3" t="n">
         <v>43455</v>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="I98" t="n">
+        <v>0.5825</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.00853912563829967</v>
+      </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
-      <c r="M98" t="n">
-        <v>0.5825</v>
-      </c>
-      <c r="N98" t="n">
-        <v>0.00853912563829967</v>
-      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
@@ -5417,10 +4000,6 @@
       <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr"/>
-      <c r="Z98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5428,7 +4007,7 @@
           <t>FAR HYC W18-02-2aPGRNoneCvRelay</t>
         </is>
       </c>
-      <c r="B99" s="1" t="n">
+      <c r="B99" s="3" t="n">
         <v>43480</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -5437,24 +4016,16 @@
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E99" t="n">
+        <v>2774.51855131863</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.78913598922001</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="n">
-        <v>2774.51855131863</v>
-      </c>
-      <c r="J99" t="n">
-        <v>0.78913598922001</v>
-      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
@@ -5467,10 +4038,6 @@
       <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
-      <c r="Z99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5478,7 +4045,7 @@
           <t>FAR HYC W18-02-2aPGRNoneCvRelay</t>
         </is>
       </c>
-      <c r="B100" s="1" t="n">
+      <c r="B100" s="3" t="n">
         <v>43495</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -5487,54 +4054,42 @@
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
+      <c r="M100" t="n">
+        <v>76.39149999999999</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.656972031368157</v>
+      </c>
+      <c r="O100" t="n">
+        <v>10.275</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.118145390656315</v>
+      </c>
       <c r="Q100" t="n">
-        <v>76.39149999999999</v>
+        <v>11.575</v>
       </c>
       <c r="R100" t="n">
-        <v>0.656972031368157</v>
+        <v>0.356779577143461</v>
       </c>
       <c r="S100" t="n">
-        <v>10.275</v>
+        <v>3.17156283783855</v>
       </c>
       <c r="T100" t="n">
-        <v>0.118145390656315</v>
+        <v>0.302461937503286</v>
       </c>
       <c r="U100" t="n">
-        <v>11.575</v>
+        <v>806.601161697189</v>
       </c>
       <c r="V100" t="n">
-        <v>0.356779577143461</v>
-      </c>
-      <c r="W100" t="n">
-        <v>3.17156283783855</v>
-      </c>
-      <c r="X100" t="n">
-        <v>0.302461937503286</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>806.601161697189</v>
-      </c>
-      <c r="Z100" t="n">
         <v>0.189206168486071</v>
       </c>
     </row>
@@ -5544,31 +4099,23 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B101" s="1" t="n">
+      <c r="B101" s="3" t="n">
         <v>43237</v>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="n">
+        <v>155</v>
+      </c>
+      <c r="H101" t="n">
+        <v>13.3853153368408</v>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="n">
-        <v>155</v>
-      </c>
-      <c r="L101" t="n">
-        <v>13.3853153368408</v>
-      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
@@ -5579,10 +4126,6 @@
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
-      <c r="Y101" t="inlineStr"/>
-      <c r="Z101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5590,33 +4133,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B102" s="1" t="n">
+      <c r="B102" s="3" t="n">
         <v>43270</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+      <c r="I102" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.0131497781983829</v>
+      </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
-      <c r="M102" t="n">
-        <v>0.4075</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0.0131497781983829</v>
-      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
@@ -5625,10 +4160,6 @@
       <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
-      <c r="Y102" t="inlineStr"/>
-      <c r="Z102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5636,33 +4167,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B103" s="1" t="n">
+      <c r="B103" s="3" t="n">
         <v>43290</v>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="I103" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.0103077640640441</v>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
-      <c r="M103" t="n">
-        <v>0.8275</v>
-      </c>
-      <c r="N103" t="n">
-        <v>0.0103077640640441</v>
-      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
@@ -5671,10 +4194,6 @@
       <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
-      <c r="Y103" t="inlineStr"/>
-      <c r="Z103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5682,33 +4201,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B104" s="1" t="n">
+      <c r="B104" s="3" t="n">
         <v>43306</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="I104" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.0158113883008419</v>
+      </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
-      <c r="M104" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="N104" t="n">
-        <v>0.0158113883008419</v>
-      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
@@ -5717,10 +4228,6 @@
       <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr"/>
-      <c r="Y104" t="inlineStr"/>
-      <c r="Z104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5728,33 +4235,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B105" s="1" t="n">
+      <c r="B105" s="3" t="n">
         <v>43341</v>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="I105" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.0147196014438797</v>
+      </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
-      <c r="M105" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0.0147196014438797</v>
-      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
@@ -5763,10 +4262,6 @@
       <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
-      <c r="Y105" t="inlineStr"/>
-      <c r="Z105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5774,29 +4269,21 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B106" s="1" t="n">
+      <c r="B106" s="3" t="n">
         <v>43364</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E106" t="n">
+        <v>364.848824829915</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.191435818438637</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="n">
-        <v>364.848824829915</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0.191435818438637</v>
-      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
@@ -5809,10 +4296,6 @@
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
-      <c r="Y106" t="inlineStr"/>
-      <c r="Z106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5820,33 +4303,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B107" s="1" t="n">
+      <c r="B107" s="3" t="n">
         <v>43381</v>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="I107" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.015545631755148</v>
+      </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
-      <c r="M107" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0.015545631755148</v>
-      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
@@ -5855,10 +4330,6 @@
       <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
-      <c r="Y107" t="inlineStr"/>
-      <c r="Z107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5866,29 +4337,21 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B108" s="1" t="n">
+      <c r="B108" s="3" t="n">
         <v>43413</v>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E108" t="n">
+        <v>1630.0760616897</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.01034059313035</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="n">
-        <v>1630.0760616897</v>
-      </c>
-      <c r="J108" t="n">
-        <v>1.01034059313035</v>
-      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
@@ -5901,10 +4364,6 @@
       <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
-      <c r="Y108" t="inlineStr"/>
-      <c r="Z108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5912,45 +4371,33 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B109" s="1" t="n">
+      <c r="B109" s="3" t="n">
         <v>43440</v>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
+      <c r="K109" t="n">
+        <v>91.9166666666667</v>
+      </c>
+      <c r="L109" t="n">
+        <v>1.81748197810618</v>
+      </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
-      <c r="O109" t="n">
-        <v>91.9166666666667</v>
-      </c>
-      <c r="P109" t="n">
-        <v>1.81748197810618</v>
-      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr"/>
-      <c r="Y109" t="inlineStr"/>
-      <c r="Z109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5958,33 +4405,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B110" s="1" t="n">
+      <c r="B110" s="3" t="n">
         <v>43446</v>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
+      <c r="I110" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.0179698822107065</v>
+      </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
-      <c r="M110" t="n">
-        <v>0.3025</v>
-      </c>
-      <c r="N110" t="n">
-        <v>0.0179698822107065</v>
-      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
@@ -5993,10 +4432,6 @@
       <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr"/>
-      <c r="Y110" t="inlineStr"/>
-      <c r="Z110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6004,33 +4439,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B111" s="1" t="n">
+      <c r="B111" s="3" t="n">
         <v>43455</v>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+      <c r="I111" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.013228756555323</v>
+      </c>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
-      <c r="M111" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="N111" t="n">
-        <v>0.013228756555323</v>
-      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
@@ -6039,10 +4466,6 @@
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr"/>
-      <c r="Y111" t="inlineStr"/>
-      <c r="Z111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6050,7 +4473,7 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B112" s="1" t="n">
+      <c r="B112" s="3" t="n">
         <v>43480</v>
       </c>
       <c r="C112" t="inlineStr">
@@ -6059,24 +4482,16 @@
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E112" t="n">
+        <v>2483.06093918149</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.37681731191883</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="n">
-        <v>2483.06093918149</v>
-      </c>
-      <c r="J112" t="n">
-        <v>1.37681731191883</v>
-      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
@@ -6089,10 +4504,6 @@
       <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
-      <c r="Y112" t="inlineStr"/>
-      <c r="Z112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6100,7 +4511,7 @@
           <t>FAR HYC W18-02-2aPGRNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B113" s="1" t="n">
+      <c r="B113" s="3" t="n">
         <v>43495</v>
       </c>
       <c r="C113" t="inlineStr">
@@ -6109,54 +4520,42 @@
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
+      <c r="M113" t="n">
+        <v>79.73350000000001</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0.244341802945521</v>
+      </c>
+      <c r="O113" t="n">
+        <v>10.725</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0.110867789130418</v>
+      </c>
       <c r="Q113" t="n">
-        <v>79.73350000000001</v>
+        <v>10.55</v>
       </c>
       <c r="R113" t="n">
-        <v>0.244341802945521</v>
+        <v>0.12583057392118</v>
       </c>
       <c r="S113" t="n">
-        <v>10.725</v>
+        <v>1.13459950593139</v>
       </c>
       <c r="T113" t="n">
-        <v>0.110867789130418</v>
+        <v>0.123813870406536</v>
       </c>
       <c r="U113" t="n">
-        <v>10.55</v>
+        <v>1018.78262861888</v>
       </c>
       <c r="V113" t="n">
-        <v>0.12583057392118</v>
-      </c>
-      <c r="W113" t="n">
-        <v>1.13459950593139</v>
-      </c>
-      <c r="X113" t="n">
-        <v>0.123813870406536</v>
-      </c>
-      <c r="Y113" t="n">
-        <v>1018.78262861888</v>
-      </c>
-      <c r="Z113" t="n">
         <v>0.287623883044671</v>
       </c>
     </row>
@@ -6166,31 +4565,23 @@
           <t>FAR HYC W18-02-2aPGRNoneCvCalabro</t>
         </is>
       </c>
-      <c r="B114" s="1" t="n">
+      <c r="B114" s="3" t="n">
         <v>43237</v>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="n">
+        <v>161.25</v>
+      </c>
+      <c r="H114" t="n">
+        <v>7.39509972887452</v>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="n">
-        <v>161.25</v>
-      </c>
-      <c r="L114" t="n">
-        <v>7.39509972887452</v>
-      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
@@ -6201,10 +4592,6 @@
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr"/>
-      <c r="Y114" t="inlineStr"/>
-      <c r="Z114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6212,33 +4599,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvCalabro</t>
         </is>
       </c>
-      <c r="B115" s="1" t="n">
+      <c r="B115" s="3" t="n">
         <v>43270</v>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+      <c r="I115" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.016583123951777</v>
+      </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
-      <c r="M115" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="N115" t="n">
-        <v>0.016583123951777</v>
-      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
@@ -6247,10 +4626,6 @@
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
-      <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr"/>
-      <c r="Y115" t="inlineStr"/>
-      <c r="Z115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6258,33 +4633,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvCalabro</t>
         </is>
       </c>
-      <c r="B116" s="1" t="n">
+      <c r="B116" s="3" t="n">
         <v>43290</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+      <c r="I116" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.014361406616345</v>
+      </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" t="n">
-        <v>0.8325</v>
-      </c>
-      <c r="N116" t="n">
-        <v>0.014361406616345</v>
-      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
@@ -6293,10 +4660,6 @@
       <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr"/>
-      <c r="X116" t="inlineStr"/>
-      <c r="Y116" t="inlineStr"/>
-      <c r="Z116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6304,33 +4667,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvCalabro</t>
         </is>
       </c>
-      <c r="B117" s="1" t="n">
+      <c r="B117" s="3" t="n">
         <v>43306</v>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+      <c r="I117" t="n">
+        <v>0.7125</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.0154784796841723</v>
+      </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
-      <c r="M117" t="n">
-        <v>0.7125</v>
-      </c>
-      <c r="N117" t="n">
-        <v>0.0154784796841723</v>
-      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
@@ -6339,10 +4694,6 @@
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
-      <c r="Y117" t="inlineStr"/>
-      <c r="Z117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6350,33 +4701,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvCalabro</t>
         </is>
       </c>
-      <c r="B118" s="1" t="n">
+      <c r="B118" s="3" t="n">
         <v>43341</v>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
+      <c r="I118" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.016583123951777</v>
+      </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
-      <c r="M118" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="N118" t="n">
-        <v>0.016583123951777</v>
-      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
@@ -6385,10 +4728,6 @@
       <c r="T118" t="inlineStr"/>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
-      <c r="X118" t="inlineStr"/>
-      <c r="Y118" t="inlineStr"/>
-      <c r="Z118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6396,29 +4735,21 @@
           <t>FAR HYC W18-02-2aPGRNoneCvCalabro</t>
         </is>
       </c>
-      <c r="B119" s="1" t="n">
+      <c r="B119" s="3" t="n">
         <v>43364</v>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E119" t="n">
+        <v>407.012883451886</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.489868446361119</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="n">
-        <v>407.012883451886</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0.489868446361119</v>
-      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
@@ -6431,10 +4762,6 @@
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr"/>
-      <c r="Y119" t="inlineStr"/>
-      <c r="Z119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6442,33 +4769,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvCalabro</t>
         </is>
       </c>
-      <c r="B120" s="1" t="n">
+      <c r="B120" s="3" t="n">
         <v>43381</v>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
+      <c r="I120" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.0104083299973307</v>
+      </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
-      <c r="M120" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="N120" t="n">
-        <v>0.0104083299973307</v>
-      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
@@ -6477,10 +4796,6 @@
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
-      <c r="W120" t="inlineStr"/>
-      <c r="X120" t="inlineStr"/>
-      <c r="Y120" t="inlineStr"/>
-      <c r="Z120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6488,29 +4803,21 @@
           <t>FAR HYC W18-02-2aPGRNoneCvCalabro</t>
         </is>
       </c>
-      <c r="B121" s="1" t="n">
+      <c r="B121" s="3" t="n">
         <v>43430</v>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E121" t="n">
+        <v>2137.0915627799</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.37364384356664</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="n">
-        <v>2137.0915627799</v>
-      </c>
-      <c r="J121" t="n">
-        <v>1.37364384356664</v>
-      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
@@ -6523,10 +4830,6 @@
       <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
-      <c r="X121" t="inlineStr"/>
-      <c r="Y121" t="inlineStr"/>
-      <c r="Z121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6534,45 +4837,33 @@
           <t>FAR HYC W18-02-2aPGRNoneCvCalabro</t>
         </is>
       </c>
-      <c r="B122" s="1" t="n">
+      <c r="B122" s="3" t="n">
         <v>43440</v>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
+      <c r="K122" t="n">
+        <v>91.8333333333333</v>
+      </c>
+      <c r="L122" t="n">
+        <v>2.41331184766372</v>
+      </c>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
-      <c r="O122" t="n">
-        <v>91.8333333333333</v>
-      </c>
-      <c r="P122" t="n">
-        <v>2.41331184766372</v>
-      </c>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr"/>
-      <c r="Y122" t="inlineStr"/>
-      <c r="Z122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6580,33 +4871,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvCalabro</t>
         </is>
       </c>
-      <c r="B123" s="1" t="n">
+      <c r="B123" s="3" t="n">
         <v>43446</v>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
+      <c r="I123" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.0217466472511665</v>
+      </c>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
-      <c r="M123" t="n">
-        <v>0.5125</v>
-      </c>
-      <c r="N123" t="n">
-        <v>0.0217466472511665</v>
-      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
@@ -6615,10 +4898,6 @@
       <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
-      <c r="W123" t="inlineStr"/>
-      <c r="X123" t="inlineStr"/>
-      <c r="Y123" t="inlineStr"/>
-      <c r="Z123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6626,33 +4905,25 @@
           <t>FAR HYC W18-02-2aPGRNoneCvCalabro</t>
         </is>
       </c>
-      <c r="B124" s="1" t="n">
+      <c r="B124" s="3" t="n">
         <v>43455</v>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
+      <c r="I124" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.0334165627596057</v>
+      </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
-      <c r="M124" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="N124" t="n">
-        <v>0.0334165627596057</v>
-      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
@@ -6661,10 +4932,6 @@
       <c r="T124" t="inlineStr"/>
       <c r="U124" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
-      <c r="W124" t="inlineStr"/>
-      <c r="X124" t="inlineStr"/>
-      <c r="Y124" t="inlineStr"/>
-      <c r="Z124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6672,7 +4939,7 @@
           <t>FAR HYC W18-02-2aPGRNoneCvCalabro</t>
         </is>
       </c>
-      <c r="B125" s="1" t="n">
+      <c r="B125" s="3" t="n">
         <v>43480</v>
       </c>
       <c r="C125" t="inlineStr">
@@ -6681,24 +4948,16 @@
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
+      <c r="E125" t="n">
+        <v>2675.25933352376</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.94332750488546</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="n">
-        <v>2675.25933352376</v>
-      </c>
-      <c r="J125" t="n">
-        <v>1.94332750488546</v>
-      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
@@ -6711,10 +4970,6 @@
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
-      <c r="W125" t="inlineStr"/>
-      <c r="X125" t="inlineStr"/>
-      <c r="Y125" t="inlineStr"/>
-      <c r="Z125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6722,7 +4977,7 @@
           <t>FAR HYC W18-02-2aPGRNoneCvCalabro</t>
         </is>
       </c>
-      <c r="B126" s="1" t="n">
+      <c r="B126" s="3" t="n">
         <v>43495</v>
       </c>
       <c r="C126" t="inlineStr">
@@ -6731,54 +4986,42 @@
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Calabro</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
+      <c r="M126" t="n">
+        <v>80.041</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.0358003724375425</v>
+      </c>
+      <c r="O126" t="n">
+        <v>10.775</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.0478713553878175</v>
+      </c>
       <c r="Q126" t="n">
-        <v>80.041</v>
+        <v>10.625</v>
       </c>
       <c r="R126" t="n">
-        <v>0.0358003724375425</v>
+        <v>0.0249999999999998</v>
       </c>
       <c r="S126" t="n">
-        <v>10.775</v>
+        <v>1.92713907364684</v>
       </c>
       <c r="T126" t="n">
-        <v>0.0478713553878175</v>
+        <v>0.173411493020798</v>
       </c>
       <c r="U126" t="n">
-        <v>10.625</v>
+        <v>1067.2182556195</v>
       </c>
       <c r="V126" t="n">
-        <v>0.0249999999999998</v>
-      </c>
-      <c r="W126" t="n">
-        <v>1.92713907364684</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0.173411493020798</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>1067.2182556195</v>
-      </c>
-      <c r="Z126" t="n">
         <v>0.300669285630632</v>
       </c>
     </row>
